--- a/stories/arbres/TREE-AUT-014.xlsx
+++ b/stories/arbres/TREE-AUT-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami est avec papa, près de la fenêtre. Sami a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute papa. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. Une feuille tombe. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le bac à sable. Une feuille tombe. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le bac à sable. Une feuille tombe. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2541,6 +2594,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2763,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de le bac à sable, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3865,6 +3958,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4029,6 +4127,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de le bac à sable, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5189,6 +5322,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5353,6 +5491,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La couverture est douce. On attend son tour. Cette fin-là est celle de le bac à sable, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6355,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le toboggan. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6493,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le toboggan. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7047,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7214,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7213,6 +7407,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7377,6 +7576,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8537,6 +8771,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8701,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9861,6 +10135,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10025,6 +10304,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10471,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10638,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10805,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10972,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11139,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10859,7 +11168,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. Un vélo passe au loin. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers les balançoires. Un vélo passe au loin. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10997,6 +11306,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers les balançoires. Un vélo passe au loin. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11885,6 +12220,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12049,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de les balançoires, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13209,6 +13584,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13373,6 +13753,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de les balançoires, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14533,6 +14948,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14697,6 +15117,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de les balançoires, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15598,6 +16048,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-014.xlsx
+++ b/stories/arbres/TREE-AUT-014.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami est avec papa, près de la fenêtre. Sami a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute papa. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Sami rejoint Tom. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de le bac à sable, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Sami rejoint Léa. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Sami rejoint Sami. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3985,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
           <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de le bac à sable, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Sami rejoint Léa. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Sami rejoint Sami. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Sami rejoint Tom. La couverture est douce. On attend son tour. Cette fin-là est celle de le bac à sable, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Sami rejoint Léa. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Sami a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Sami a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Sami a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>narrateur|Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de les balançoires, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de les balançoires, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de les balançoires, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16055,6 +16146,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16069,7 +16174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16256,6 +16361,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-014.xlsx
+++ b/stories/arbres/TREE-AUT-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — près de la fenêtre</t>
+          <t>La goutte sur la vitre</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Nino regarde le parc depuis la vitre. Il va jouer, puis, avant de rentrer, il cherche son seau, son manteau, son doudou, et il les prend.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sami est avec papa, près de la fenêtre. Sami a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute papa. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>La pluie vient juste de s'arrêter. Sur la vitre, une goutte glisse, toute seule. Elle laisse un trait brillant. Derrière la goutte, le parc est mouillé. Les balançoires luisent. Le bac à sable est sombre, comme du chocolat. Près du radiateur, l'air est tiède. Un manteau bleu pend au crochet. Le crochet fait un petit toc. Un seau jaune attend près des chaussures. Le seau a encore un peu de sable au fond. Un doudou gris est sur la chaise. Regarde, Nino. La goutte. Le parc est à nous, tout à l'heure. En ce moment, Nino pose le nez sur le verre. Le verre est froid. Je veux jouer. On y va. Et avant de partir, on reprend tes affaires. Nino va reprendre ses affaires, avant de partir. Nino hoche la tête. Le seau l'attend. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,36 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sami est avec papa, près de la fenêtre. Sami a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami écoute papa. Sami entend les mots : reprendre ses affaires, avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La pluie vient juste de s'arrêter.
+narrateur|Sur la vitre, une goutte glisse, toute seule.
+narrateur|Elle laisse un trait brillant.
+narrateur|Derrière la goutte, le parc est mouillé.
+narrateur|Les balançoires luisent.
+narrateur|Le bac à sable est sombre, comme du chocolat.
+narrateur|Près du radiateur, l'air est tiède.
+narrateur|Un manteau bleu pend au crochet.
+narrateur|Le crochet fait un petit toc.
+narrateur|Un seau jaune attend près des chaussures.
+narrateur|Le seau a encore un peu de sable au fond.
+narrateur|Un doudou gris est sur la chaise.
+maman|Regarde, Nino. La goutte.
+papa|Le parc est à nous, tout à l'heure.
+narrateur|En ce moment, Nino pose le nez sur le verre.
+narrateur|Le verre est froid.
+enfant-m|Je veux jouer.
+maman|On y va.
+papa|Et avant de partir, on reprend tes affaires.
+narrateur|Nino va reprendre ses affaires, avant de partir.
+narrateur|Nino hoche la tête.
+narrateur|Le seau l'attend.
+narrateur|Le manteau aussi.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,radiateur</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Le parc a trois coins tout proches. Le bac à sable, le toboggan, ou les balançoires ? On joue. Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1559,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Le parc a trois coins tout proches.
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|On joue. Après, on reprend tes affaires.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. Une feuille tombe. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Nino s'agenouille au bord du bac. Le sable est frais, encore un peu mouillé. Ça fait chh quand la main entre. Le seau jaune sonne contre le bois. Un château, papa. D'accord. Le seau reste près de toi. Le manteau est sur le banc. Nino verse le sable. Ça sent la terre propre. Un grain reste sous son ongle. Quand ce sera l'heure, on cherche seau et manteau. On les prend, avant de partir. Nino appuie le château avec la paume. Bravo. Tu joues, et tes affaires t'attendent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1729,26 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le bac à sable. Une feuille tombe. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino s'agenouille au bord du bac.
+narrateur|Le sable est frais, encore un peu mouillé.
+narrateur|Ça fait chh quand la main entre.
+narrateur|Le seau jaune sonne contre le bois.
+enfant-m|Un château, papa.
+papa|D'accord. Le seau reste près de toi.
+maman|Le manteau est sur le banc.
+narrateur|Nino verse le sable. Ça sent la terre propre.
+narrateur|Un grain reste sous son ongle.
+papa|Quand ce sera l'heure, on cherche seau et manteau.
+maman|On les prend, avant de partir.
+narrateur|Nino appuie le château avec la paume.
+papa|Bravo. Tu joues, et tes affaires t'attendent.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>C'est bientôt l'heure de rentrer. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1933,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|C'est bientôt l'heure de rentrer.
+papa|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. Reprendre ses affaires, avant de partir. On cherche le seau. On cherche le manteau. On les prend. Nino essuie un grain de sable sur sa joue. Le seau, puis le manteau. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2106,11 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>maman|Oui. Reprendre ses affaires, avant de partir.
+papa|On cherche le seau. On cherche le manteau. On les prend.
+narrateur|Nino essuie un grain de sable sur sa joue.
+enfant-m|Le seau, puis le manteau.
+maman|Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2078,7 +2138,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Nino peut encore jouer un peu, près de ses affaires. Les cubes, le livre, ou la dînette ? On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2246,7 +2306,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Nino peut encore jouer un peu, près de ses affaires.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2274,7 +2336,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Près du bac, les cubes sont un peu sableux. Nino en pose un, puis un autre. Un mur pour le château. Le seau reste à ta droite. Le manteau reste sur le banc. Le cube rouge a un grain de sable dessus. Quand le mur est fini, on reprend tes affaires. Nino termine le mur. Bravo. Avant de partir, on les prend.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2414,7 +2476,15 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Près du bac, les cubes sont un peu sableux.
+narrateur|Nino en pose un, puis un autre.
+enfant-m|Un mur pour le château.
+papa|Le seau reste à ta droite.
+maman|Le manteau reste sur le banc.
+narrateur|Le cube rouge a un grain de sable dessus.
+papa|Quand le mur est fini, on reprend tes affaires.
+narrateur|Nino termine le mur.
+maman|Bravo. Avant de partir, on les prend.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2442,7 +2512,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2610,7 +2680,9 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2638,7 +2710,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de le bac à sable, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau bleu a un grain de sable à la manche. Nino le prend au banc. Bravo. Maintenant le seau. Il est jaune. Je le prends. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2778,7 +2850,18 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Un chat miaule une fois. On attend son tour. Cette fin-là est celle de le bac à sable, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau bleu a un grain de sable à la manche.
+narrateur|Nino le prend au banc.
+papa|Bravo. Maintenant le seau.
+enfant-m|Il est jaune. Je le prends.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2806,7 +2889,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2946,7 +3029,10 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2974,7 +3060,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau jaune sonne. Il y a encore du sable au fond. Nino le soulève à deux mains. Oui. Ensuite le manteau. On reprend tes affaires, avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3114,7 +3200,18 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau jaune sonne. Il y a encore du sable au fond.
+narrateur|Nino le soulève à deux mains.
+maman|Oui. Ensuite le manteau.
+papa|On reprend tes affaires, avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3142,7 +3239,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3282,7 +3379,10 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3310,7 +3410,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou gris a une odeur de vent. Nino le serre, puis prend le seau. Le manteau aussi. J'ai tout. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3450,7 +3550,18 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou gris a une odeur de vent.
+narrateur|Nino le serre, puis prend le seau.
+maman|Le manteau aussi.
+enfant-m|J'ai tout.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3478,7 +3589,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3618,7 +3729,10 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3646,7 +3760,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Près du bac, le livre a un coin un peu rêche. Nino l'ouvre sur ses genoux. Un crabe ! Oui. Ton seau est juste là, jaune. Ton manteau est sur le banc, bleu. Nino referme le livre. On garde le livre. Et on reprend tes affaires. Avant de partir. Le sable fait un petit tas contre le seau.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3786,7 +3900,15 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Près du bac, le livre a un coin un peu rêche.
+narrateur|Nino l'ouvre sur ses genoux.
+enfant-m|Un crabe !
+maman|Oui. Ton seau est juste là, jaune.
+papa|Ton manteau est sur le banc, bleu.
+narrateur|Nino referme le livre.
+maman|On garde le livre. Et on reprend tes affaires.
+papa|Avant de partir.
+narrateur|Le sable fait un petit tas contre le seau.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3814,7 +3936,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3982,7 +4104,9 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4010,7 +4134,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de le bac à sable, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau est un peu humide, encore. Nino le boutonne, une boutonnière après l'autre. Tu as le manteau. Cherche le seau. Il est près du livre. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4150,7 +4274,18 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On attend son tour. Cette fin-là est celle de le bac à sable, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau est un peu humide, encore.
+narrateur|Nino le boutonne, une boutonnière après l'autre.
+papa|Tu as le manteau. Cherche le seau.
+maman|Il est près du livre.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4178,7 +4313,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4318,7 +4453,10 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4346,7 +4484,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau attend contre le livre fermé. Nino le prend. Le livre rentre dans le sac. Le manteau, maintenant. Avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4486,7 +4624,18 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau attend contre le livre fermé.
+narrateur|Nino le prend. Le livre rentre dans le sac.
+maman|Le manteau, maintenant.
+papa|Avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4514,7 +4663,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4654,7 +4803,10 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4682,7 +4834,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était sous le livre. Nino le sort, tout doux. Puis le seau. Puis le manteau. Avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4822,7 +4974,18 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou était sous le livre.
+narrateur|Nino le sort, tout doux.
+papa|Puis le seau. Puis le manteau.
+enfant-m|Avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4850,7 +5013,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4990,7 +5153,10 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5018,7 +5184,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>Près du bac, la dînette est dans un panier. Nino pose une tasse sur le rebord. Du sable-thé. La tasse jouet, oui. Le seau, on le reprend. Ce n'est pas la même chose. Nino range la tasse. On cherche seau et manteau. On les prend. Avant de partir. Le château reste, tout petit, dans le bac.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5158,7 +5324,15 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Près du bac, la dînette est dans un panier.
+narrateur|Nino pose une tasse sur le rebord.
+enfant-m|Du sable-thé.
+papa|La tasse jouet, oui. Le seau, on le reprend.
+maman|Ce n'est pas la même chose.
+narrateur|Nino range la tasse.
+papa|On cherche seau et manteau. On les prend.
+maman|Avant de partir.
+narrateur|Le château reste, tout petit, dans le bac.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5186,7 +5360,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5354,7 +5528,9 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5382,7 +5558,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. La couverture est douce. On attend son tour. Cette fin-là est celle de le bac à sable, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau glisse du banc. Nino le rattrape. La dînette est déjà dans le panier. Bravo. Le seau, maintenant. On les prend tous, avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5522,7 +5698,18 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. La couverture est douce. On attend son tour. Cette fin-là est celle de le bac à sable, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau glisse du banc. Nino le rattrape.
+narrateur|La dînette est déjà dans le panier.
+maman|Bravo. Le seau, maintenant.
+papa|On les prend tous, avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5550,7 +5737,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5690,7 +5877,10 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5718,7 +5908,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau sert de couvercle un moment, puis Nino le vide. Le sable retombe dans le bac. Le seau est à toi. On le prend. Le manteau t'attend. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5858,7 +6048,18 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau sert de couvercle un moment, puis Nino le vide.
+narrateur|Le sable retombe dans le bac.
+papa|Le seau est à toi. On le prend.
+maman|Le manteau t'attend.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5886,7 +6087,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6026,7 +6227,10 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6054,7 +6258,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le bac à sable. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était dans le panier, sous une tasse. Nino le sort. La tasse reste. Tes affaires, pas la dînette du parc. Seau, manteau, doudou. Bravo. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6194,7 +6398,18 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le bac à sable.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou était dans le panier, sous une tasse.
+narrateur|Nino le sort. La tasse reste.
+maman|Tes affaires, pas la dînette du parc.
+papa|Seau, manteau, doudou. Bravo.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6222,7 +6437,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6362,7 +6577,10 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6390,7 +6608,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Le toboggan brille encore de pluie. Les marches sont froides sous la main. Nino pose le pied, une marche après l'autre. Je glisse ! J'attends en bas. Ton manteau est sur le crochet. Le seau est près des chaussures. Nino glisse. Le plastique fait un petit frou. Ses pieds retrouvent l'herbe mouillée. Encore une fois, puis on reprend tes affaires. Nino souffle. Il a les joues tièdes. Avant de partir, on cherche seau et manteau. On les prend. Bravo d'avoir attendu ta descente.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6530,8 +6748,18 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers le toboggan. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Le toboggan brille encore de pluie.
+narrateur|Les marches sont froides sous la main.
+narrateur|Nino pose le pied, une marche après l'autre.
+enfant-m|Je glisse !
+papa|J'attends en bas. Ton manteau est sur le crochet.
+maman|Le seau est près des chaussures.
+narrateur|Nino glisse. Le plastique fait un petit frou.
+narrateur|Ses pieds retrouvent l'herbe mouillée.
+papa|Encore une fois, puis on reprend tes affaires.
+narrateur|Nino souffle. Il a les joues tièdes.
+maman|Avant de partir, on cherche seau et manteau.
+papa|On les prend. Bravo d'avoir attendu ta descente.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6559,7 +6787,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>C'est bientôt l'heure de rentrer. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6719,7 +6947,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|C'est bientôt l'heure de rentrer.
+papa|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6747,7 +6976,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. Reprendre ses affaires, avant de partir. On cherche le seau. On cherche le manteau. On les prend. Nino secoue une goutte de sa manche. Le seau, puis le manteau. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6891,7 +7120,11 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>maman|Oui. Reprendre ses affaires, avant de partir.
+papa|On cherche le seau. On cherche le manteau. On les prend.
+narrateur|Nino secoue une goutte de sa manche.
+enfant-m|Le seau, puis le manteau.
+maman|Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6919,7 +7152,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Nino peut encore jouer un peu, près de ses affaires. Les cubes, le livre, ou la dînette ? On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7087,7 +7320,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Nino peut encore jouer un peu, près de ses affaires.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7115,7 +7350,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Au pied du toboggan, les cubes attendent sur un linge. Le linge est encore humide. Une tour basse. D'accord. Tes affaires restent près de papa. Nino empile deux cubes. Je vois le seau. Je vois le manteau. Toi aussi, tu peux les chercher des yeux. Nino montre le crochet, sans se lever trop vite. Bravo. On les prendra avant de partir.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7255,7 +7490,15 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Au pied du toboggan, les cubes attendent sur un linge.
+narrateur|Le linge est encore humide.
+enfant-m|Une tour basse.
+maman|D'accord. Tes affaires restent près de papa.
+narrateur|Nino empile deux cubes.
+papa|Je vois le seau. Je vois le manteau.
+maman|Toi aussi, tu peux les chercher des yeux.
+narrateur|Nino montre le crochet, sans se lever trop vite.
+papa|Bravo. On les prendra avant de partir.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7283,7 +7526,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7451,7 +7694,9 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7479,7 +7724,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Au crochet du toboggan, le manteau fait toc. Nino le décroche. Bien. Le seau est près des chaussures. Je le prends aussi. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7619,7 +7864,18 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Au crochet du toboggan, le manteau fait toc.
+narrateur|Nino le décroche.
+papa|Bien. Le seau est près des chaussures.
+enfant-m|Je le prends aussi.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7647,7 +7903,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7787,7 +8043,10 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7815,7 +8074,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau a reçu une goutte du toboggan. Nino l'essuie sur l'herbe, tout doux. On le prend. Ensuite le manteau. Avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7955,7 +8214,18 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau a reçu une goutte du toboggan.
+narrateur|Nino l'essuie sur l'herbe, tout doux.
+maman|On le prend. Ensuite le manteau.
+papa|Avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7983,7 +8253,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8123,7 +8393,10 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8151,7 +8424,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était dans le sac, au pied de la rampe. Nino le retrouve au premier regard. Bravo. Tu as cherché, tu as pris. Le seau et le manteau aussi. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8291,7 +8564,18 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou était dans le sac, au pied de la rampe.
+narrateur|Nino le retrouve au premier regard.
+maman|Bravo. Tu as cherché, tu as pris.
+papa|Le seau et le manteau aussi.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8319,7 +8603,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8459,7 +8743,10 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8487,7 +8774,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Au toboggan, le livre reste dans le sac de papa. Nino le sort. Les pages sentent le tissu. Une page, puis l'autre. Comme tes affaires. On les reprend, une puis l'autre. Seau. Manteau. Doudou. Nino pose le livre sur le sac. Bravo. Tu as fini la page. Avant de partir, on cherche, puis on prend. Le toboggan sèche au soleil, tout lentement.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8627,7 +8914,15 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Au toboggan, le livre reste dans le sac de papa.
+narrateur|Nino le sort. Les pages sentent le tissu.
+enfant-m|Une page, puis l'autre.
+papa|Comme tes affaires. On les reprend, une puis l'autre.
+maman|Seau. Manteau. Doudou.
+narrateur|Nino pose le livre sur le sac.
+papa|Bravo. Tu as fini la page.
+maman|Avant de partir, on cherche, puis on prend.
+narrateur|Le toboggan sèche au soleil, tout lentement.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8655,7 +8950,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8823,7 +9118,9 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8851,7 +9148,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau couvre un instant le livre, puis Nino le met. Le tissu est frais sur les bras. Affaires reprises. On rentre. Bravo, Nino. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8991,7 +9288,18 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau couvre un instant le livre, puis Nino le met.
+narrateur|Le tissu est frais sur les bras.
+papa|Affaires reprises.
+maman|On rentre. Bravo, Nino.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9019,7 +9327,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9159,7 +9467,10 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9187,7 +9498,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau pend au sac, à côté du livre. Nino le décroche. Tu as le seau. Cherche le manteau. Au crochet. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9327,7 +9638,18 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau pend au sac, à côté du livre.
+narrateur|Nino le décroche.
+maman|Tu as le seau. Cherche le manteau.
+enfant-m|Au crochet.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9355,7 +9677,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9495,7 +9817,10 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9523,7 +9848,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou sent encore le tissu du sac. Nino le serre. Le livre est déjà rangé. Manteau. Seau. Doudou. Avant de partir, c'est fait. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9663,7 +9988,18 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou sent encore le tissu du sac.
+narrateur|Nino le serre. Le livre est déjà rangé.
+papa|Manteau. Seau. Doudou.
+maman|Avant de partir, c'est fait.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9691,7 +10027,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9831,7 +10167,10 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9859,7 +10198,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>Au toboggan, la dînette cliquette dans le sac. Nino sort une assiette ronde. Pour le goûter plus tard. Oui. D'abord tes affaires de parc. Le manteau. Le seau. Le doudou. Nino remet l'assiette dans le sac. Bravo. Tu as rangé. Avant de partir, on reprend ce qui est à toi. L'herbe mouillée brille encore.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9999,7 +10338,15 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Au toboggan, la dînette cliquette dans le sac.
+narrateur|Nino sort une assiette ronde.
+enfant-m|Pour le goûter plus tard.
+maman|Oui. D'abord tes affaires de parc.
+papa|Le manteau. Le seau. Le doudou.
+narrateur|Nino remet l'assiette dans le sac.
+maman|Bravo. Tu as rangé.
+papa|Avant de partir, on reprend ce qui est à toi.
+narrateur|L'herbe mouillée brille encore.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10027,7 +10374,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10195,7 +10542,9 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10223,7 +10572,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau était sous le sac de dînette. Nino le tire, tout droit. Tu as cherché. Bravo. Le seau, ensuite. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10363,7 +10712,18 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau était sous le sac de dînette.
+narrateur|Nino le tire, tout droit.
+papa|Tu as cherché. Bravo.
+maman|Le seau, ensuite.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10391,7 +10751,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10531,7 +10891,10 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10559,7 +10922,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau a servi de siège un moment. Nino se lève et le prend. Oui. C'est le tien. On reprend tes affaires, avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10699,7 +11062,18 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau a servi de siège un moment.
+narrateur|Nino se lève et le prend.
+maman|Oui. C'est le tien.
+papa|On reprend tes affaires, avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10727,7 +11101,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10867,7 +11241,10 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10895,7 +11272,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte le toboggan. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était assis dans une assiette jouet. Nino rit un peu, puis le prend. L'assiette rentre. Le doudou aussi. Et le manteau. Et le seau. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11035,7 +11412,18 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte le toboggan.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou était assis dans une assiette jouet.
+narrateur|Nino rit un peu, puis le prend.
+papa|L'assiette rentre. Le doudou aussi.
+maman|Et le manteau. Et le seau.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11063,7 +11451,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11203,7 +11591,10 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11231,7 +11622,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. Un vélo passe au loin. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>Les chaînes des balançoires sont froides. Elles font un bruit de goutte, tout léger. Nino s'assoit. Le siège est encore humide. Un peu, maman. Je pousse tout doux. Le manteau reste sur le crochet du poteau. Nino avance, puis revient. Le vent lui touche le nez. Le seau est sous le banc. Quand on s'arrête, on reprend tes affaires, avant de partir. Nino pose les pieds par terre. Bravo. Tu t'es arrêté tout seul. Une flaque reflète le ciel, tout près.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11371,11 +11762,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sami va vers les balançoires. Un vélo passe au loin. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On rit un peu.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Les chaînes des balançoires sont froides.
+narrateur|Elles font un bruit de goutte, tout léger.
+narrateur|Nino s'assoit. Le siège est encore humide.
+enfant-m|Un peu, maman.
+maman|Je pousse tout doux.
+papa|Le manteau reste sur le crochet du poteau.
+narrateur|Nino avance, puis revient.
+narrateur|Le vent lui touche le nez.
+maman|Le seau est sous le banc.
+papa|Quand on s'arrête, on reprend tes affaires, avant de partir.
+narrateur|Nino pose les pieds par terre.
+maman|Bravo. Tu t'es arrêté tout seul.
+narrateur|Une flaque reflète le ciel, tout près.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>chaine</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11400,7 +11806,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>C'est bientôt l'heure de rentrer. Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11560,7 +11966,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>narrateur|C'est bientôt l'heure de rentrer.
+papa|Avant de partir, on fait quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11588,7 +11995,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. Reprendre ses affaires, avant de partir. On cherche le seau. On cherche le manteau. On les prend. Nino pose les deux pieds dans l'herbe. Le seau, puis le manteau. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11732,7 +12139,11 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sami respire. Sami retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>maman|Oui. Reprendre ses affaires, avant de partir.
+papa|On cherche le seau. On cherche le manteau. On les prend.
+narrateur|Nino pose les deux pieds dans l'herbe.
+enfant-m|Le seau, puis le manteau.
+maman|Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11760,7 +12171,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Nino peut encore jouer un peu, près de ses affaires. Les cubes, le livre, ou la dînette ? On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11928,7 +12339,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Nino peut encore jouer un peu, près de ses affaires.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On joue. Puis on reprend ce qui t'appartient.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11956,7 +12369,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Sous les balançoires, les cubes sont dans un sac. Nino les sort, un par un. Un chemin de cubes. Le doudou est sur la chaise, plus loin. Le manteau est au crochet. Le seau sous le banc. Nino aligne trois cubes vers le banc. Ce chemin mène à tes affaires. Avant de partir, on les reprend. Nino hoche la tête. Une goutte tombe d'une chaîne.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12096,7 +12509,15 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>narrateur|Sous les balançoires, les cubes sont dans un sac.
+narrateur|Nino les sort, un par un.
+enfant-m|Un chemin de cubes.
+papa|Le doudou est sur la chaise, plus loin.
+maman|Le manteau est au crochet. Le seau sous le banc.
+narrateur|Nino aligne trois cubes vers le banc.
+papa|Ce chemin mène à tes affaires.
+maman|Avant de partir, on les reprend.
+narrateur|Nino hoche la tête. Une goutte tombe d'une chaîne.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12124,7 +12545,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12292,7 +12713,9 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12320,7 +12743,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de les balançoires, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau quitte le crochet du poteau. Une chaîne de balançoire tinte. Tu l'as. Le seau est sous le banc. Je me baisse. Je le prends. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12460,7 +12883,18 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de les balançoires, les cubes et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau quitte le crochet du poteau.
+narrateur|Une chaîne de balançoire tinte.
+papa|Tu l'as. Le seau est sous le banc.
+enfant-m|Je me baisse. Je le prends.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12488,7 +12922,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12628,7 +13062,10 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12656,7 +13093,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Sous le banc, le seau a une feuille dedans. Nino sort la feuille. Il garde le seau. Bravo. Le manteau, maintenant. Avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12796,7 +13233,18 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, les cubes et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Sous le banc, le seau a une feuille dedans.
+narrateur|Nino sort la feuille. Il garde le seau.
+maman|Bravo. Le manteau, maintenant.
+papa|Avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12824,7 +13272,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12964,7 +13412,10 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12992,7 +13443,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était sur la chaise, un peu loin. Nino marche jusqu'à la chaise, sans courir. Tu l'as retrouvé. Seau et manteau aussi. On rentre. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13132,7 +13583,18 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, les cubes et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou était sur la chaise, un peu loin.
+narrateur|Nino marche jusqu'à la chaise, sans courir.
+papa|Tu l'as retrouvé.
+maman|Seau et manteau aussi. On rentre.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13160,7 +13622,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13300,7 +13762,10 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13328,7 +13793,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Sur la balançoire arrêtée, Nino tient le livre. Une image montre un manteau et un seau. Comme moi ! Oui. Les tiens t'attendent. Montre-les-moi, des yeux. Nino regarde le crochet. Puis le banc. Bravo. Tu as retrouvé la place. Avant de partir, on les prend. Les chaînes ne bougent plus.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13468,7 +13933,15 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>narrateur|Sur la balançoire arrêtée, Nino tient le livre.
+narrateur|Une image montre un manteau et un seau.
+enfant-m|Comme moi !
+maman|Oui. Les tiens t'attendent.
+papa|Montre-les-moi, des yeux.
+narrateur|Nino regarde le crochet. Puis le banc.
+maman|Bravo. Tu as retrouvé la place.
+papa|Avant de partir, on les prend.
+narrateur|Les chaînes ne bougent plus.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13496,7 +13969,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13664,7 +14137,9 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13692,7 +14167,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de les balançoires, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau et le livre rentrent ensemble dans les bras. Nino sent le tissu froid et le papier. Le seau ? Sous le banc. Je le prends. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13832,7 +14307,18 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de les balançoires, le livre et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau et le livre rentrent ensemble dans les bras.
+narrateur|Nino sent le tissu froid et le papier.
+maman|Le seau ?
+enfant-m|Sous le banc. Je le prends.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13860,7 +14346,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14000,7 +14486,10 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14028,7 +14517,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau tapote la jambe de Nino. Le livre est déjà dans le sac de papa. Manteau, ensuite. On reprend tes affaires, avant de partir. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14168,7 +14657,18 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le livre et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau tapote la jambe de Nino.
+narrateur|Le livre est déjà dans le sac de papa.
+papa|Manteau, ensuite.
+maman|On reprend tes affaires, avant de partir.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14196,7 +14696,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14336,7 +14836,10 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14364,7 +14867,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou a vu l'image du livre, tout à l'heure. Maintenant il est contre la joue de Nino. Cherche encore le seau et le manteau. Les voilà. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14504,7 +15007,18 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le livre et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou a vu l'image du livre, tout à l'heure.
+narrateur|Maintenant il est contre la joue de Nino.
+papa|Cherche encore le seau et le manteau.
+enfant-m|Les voilà.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14532,7 +15046,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14672,7 +15186,10 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14700,7 +15217,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>Sous les balançoires, Nino pose deux assiettes jouets. Une fourmi les contourne. Un pique-nique. Un tout petit. Puis on rentre. Tes affaires d'abord. Nino empile les assiettes. On cherche. On prend. Avant de partir. Bravo, Nino. Une flaque tremble quand il se lève.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14840,7 +15357,15 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sami répète tout bas : reprendre ses affaires, avant de partir. On range un objet. maman n'est pas loin.</t>
+          <t>narrateur|Sous les balançoires, Nino pose deux assiettes jouets.
+narrateur|Une fourmi les contourne.
+enfant-m|Un pique-nique.
+papa|Un tout petit. Puis on rentre.
+maman|Tes affaires d'abord.
+narrateur|Nino empile les assiettes.
+papa|On cherche. On prend. Avant de partir.
+maman|Bravo, Nino.
+narrateur|Une flaque tremble quand il se lève.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14868,7 +15393,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste à reprendre une affaire, puis les autres. On prend d'abord le manteau, le seau, ou le doudou ? On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15036,7 +15561,9 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Il reste à reprendre une affaire, puis les autres.
+maman|On prend d'abord le manteau, le seau, ou le doudou ?
+papa|On cherche. Ensuite on prend. Avant de partir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15064,7 +15591,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de les balançoires, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le manteau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le manteau recouvre un instant les assiettes jouets. Nino le met. Les assiettes rentrent. Bravo. Tes affaires d'abord. Le seau sous le banc. On le prend. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15204,7 +15731,18 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de les balançoires, la dînette et Tom. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le manteau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le manteau recouvre un instant les assiettes jouets.
+narrateur|Nino le met. Les assiettes rentrent.
+maman|Bravo. Tes affaires d'abord.
+papa|Le seau sous le banc. On le prend.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15232,7 +15770,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15372,7 +15910,10 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15400,7 +15941,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le seau. On cherche. On prend. Reprendre ses affaires, avant de partir. Le seau porte une cuillère de dînette. Nino pose la cuillère, garde le seau. Oui. Le seau est à toi. Manteau et doudou, ensuite. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15540,7 +16081,18 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, la dînette et Léa. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le seau.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le seau porte une cuillère de dînette.
+narrateur|Nino pose la cuillère, garde le seau.
+papa|Oui. Le seau est à toi.
+maman|Manteau et doudou, ensuite.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15568,7 +16120,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15708,7 +16260,10 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15736,7 +16291,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou a une goutte sur l'oreille. Nino l'essuie, puis serre le seau. Le manteau aussi. Avant de partir, tout est dans tes mains. Bravo. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15876,7 +16431,18 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, la dînette et Sami. Sami a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sami a entendu : reprendre ses affaires, avant de partir. Sami dit merci à papa. On rentre.</t>
+          <t>narrateur|Nino quitte les balançoires.
+narrateur|Il cherche d'abord le doudou.
+papa|On cherche. On prend.
+maman|Reprendre ses affaires, avant de partir.
+narrateur|Le doudou a une goutte sur l'oreille.
+narrateur|Nino l'essuie, puis serre le seau.
+maman|Le manteau aussi.
+papa|Avant de partir, tout est dans tes mains. Bravo.
+narrateur|Nino a le seau, le manteau, le doudou.
+narrateur|La goutte sur la vitre n'est plus là.
+enfant-m|On rentre.
+papa|Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15904,7 +16470,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as repris tes affaires, avant de partir. Nino reprend ses affaires. Bravo, Nino. On rentre ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16044,7 +16610,10 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as repris tes affaires, avant de partir.
+narrateur|Nino reprend ses affaires.
+papa|Bravo, Nino. On rentre ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16066,7 +16635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16160,6 +16729,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-014.xlsx
+++ b/stories/arbres/TREE-AUT-014.xlsx
@@ -13443,7 +13443,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nino quitte les balançoires. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était sur la chaise, un peu loin. Nino marche jusqu'à la chaise, sans courir. Tu l'as retrouvé. Seau et manteau aussi. On rentre. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
+          <t>Nino quitte les balançoires. Il cherche d'abord le doudou. On cherche. On prend. Reprendre ses affaires, avant de partir. Le doudou était sur la chaise, un peu loin. Nino marche jusqu'à la chaise, tout doux. Tu l'as retrouvé. Seau et manteau aussi. On rentre. Nino a le seau, le manteau, le doudou. La goutte sur la vitre n'est plus là. On rentre. Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13588,7 +13588,7 @@
 papa|On cherche. On prend.
 maman|Reprendre ses affaires, avant de partir.
 narrateur|Le doudou était sur la chaise, un peu loin.
-narrateur|Nino marche jusqu'à la chaise, sans courir.
+narrateur|Nino marche jusqu'à la chaise, tout doux.
 papa|Tu l'as retrouvé.
 maman|Seau et manteau aussi. On rentre.
 narrateur|Nino a le seau, le manteau, le doudou.
@@ -16635,7 +16635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16734,6 +16734,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
